--- a/data/raw/sales/Week 13/Audio_Array/other_channels.xlsx
+++ b/data/raw/sales/Week 13/Audio_Array/other_channels.xlsx
@@ -958,7 +958,7 @@
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>AH-60 BL</t>
+          <t>AH-60-BL</t>
         </is>
       </c>
       <c r="D14" s="18" t="n">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>AI-04</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="E5" s="18" t="n">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>UB-01</t>
+          <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
         </is>
       </c>
       <c r="D11" s="24" t="n">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>UB-02</t>
+          <t>UB-02 (AM-S1 + AA-21)</t>
         </is>
       </c>
       <c r="D12" s="24" t="n">
